--- a/1. RAG/data/4_testing/range_of_k/RAG_eval_k=7.xlsx
+++ b/1. RAG/data/4_testing/range_of_k/RAG_eval_k=7.xlsx
@@ -548,35 +548,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>I don't have enough information to answer that.</t>
+          <t>According to the provided context, 2% of gay men in Germany reported feeling discriminated against in the past year when showing their ID or any official document that identifies their sex.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.571</v>
+        <v>0.857</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7144</v>
+        <v>0.7181</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.63</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>61.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="3">
@@ -590,7 +590,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Lesbian women in France feel that 18% are always open about their identity, 54% are selectively open, and 28% hide their LGBT identity at work.</t>
+          <t>According to the context provided, in France, lesbian women show varying levels of comfort about being open regarding their identity at work. Specifically, 18% of lesbian respondents reported being "always open," while 54% described themselves as "selectively open." Additionally, 28% indicated that they hide their LGBT identity. This suggests that while a significant portion of lesbian women in France feel comfortable being open, a majority prefer to be selectively open rather than fully disclosing their identity.</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -603,22 +603,22 @@
         <v>0.857</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.6972</v>
+        <v>0.6973</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="I3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.5</v>
+        <v>0.196</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.733</v>
+        <v>0.867</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>42.7</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="4">
@@ -645,7 +645,7 @@
         <v>0.857</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7064</v>
+        <v>0.6657</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>8</v>
@@ -726,10 +726,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.714</v>
+        <v>0.857</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5737</v>
+        <v>0.5777</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>8</v>
@@ -807,13 +807,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.714</v>
+        <v>0.857</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5132</v>
+        <v>0.51</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>8</v>
@@ -852,10 +852,10 @@
         <v>2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.714</v>
+        <v>0.857</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.609</v>
+        <v>0.3295</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.182</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_b_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E2" s="2" t="b">
@@ -949,7 +949,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_b — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Gay? | Germany responses (Transgender): Yes: 39%, No: 55%, Don`t know: 6%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,13 @@
       <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -993,7 +989,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E4" s="2" t="b">
@@ -1001,7 +997,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1013,17 @@
       <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1039,17 @@
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1067,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E7" s="4" t="b">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E8" s="2" t="b">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1190,11 @@
       <c r="C12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="b">
         <v>1</v>
       </c>
@@ -1296,7 +1304,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1326,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1334,13 +1342,17 @@
       <c r="C18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1370,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E19" s="4" t="b">
@@ -1366,7 +1378,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1396,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E20" s="2" t="b">
@@ -1392,7 +1404,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1422,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E21" s="4" t="b">
@@ -1418,7 +1430,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1448,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E22" s="2" t="b">
@@ -1444,7 +1456,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1630,24 +1642,22 @@
       <c r="C30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1663,24 +1673,22 @@
       <c r="C31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E31" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1696,28 +1704,18 @@
       <c r="C32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1733,28 +1731,18 @@
       <c r="C33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D33" s="5" t="inlineStr"/>
       <c r="E33" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1760,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E34" s="2" t="b">
@@ -1780,18 +1768,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1807,24 +1789,22 @@
       <c r="C35" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1840,24 +1820,22 @@
       <c r="C36" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1851,11 @@
       <c r="C37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="b">
         <v>0</v>
       </c>
@@ -2025,7 +2007,11 @@
       <c r="C42" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="b">
         <v>1</v>
       </c>
@@ -2085,25 +2071,28 @@
       <c r="C44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2119,25 +2108,28 @@
       <c r="C45" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2153,29 +2145,24 @@
       <c r="C46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2191,29 +2178,24 @@
       <c r="C47" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D47" s="5" t="inlineStr"/>
       <c r="E47" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2229,29 +2211,24 @@
       <c r="C48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2246,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E49" s="4" t="b">
@@ -2277,19 +2254,18 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2307,23 +2283,26 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E50" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -2345,19 +2324,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2373,29 +2340,13 @@
       <c r="C52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
-        </is>
-      </c>
+      <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2364,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E53" s="4" t="b">
@@ -2421,19 +2372,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2390,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E54" s="2" t="b">
@@ -2459,19 +2398,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2416,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E55" s="4" t="b">
@@ -2497,19 +2424,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2527,26 +2442,15 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E56" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2468,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E57" s="4" t="b">
@@ -2572,18 +2476,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
